--- a/Data/MaKho_MaVV.xlsx
+++ b/Data/MaKho_MaVV.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_BB\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF02DFD1-7B65-4925-BFC4-8066F32A132B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8BE4E8-3037-473A-9223-B8116E47A64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
   <si>
     <t>Tên kho</t>
   </si>
@@ -196,6 +196,12 @@
   </si>
   <si>
     <t>HH005QN</t>
+  </si>
+  <si>
+    <t>Xăng E10 RON95 Mức 3</t>
+  </si>
+  <si>
+    <t>HH051-043</t>
   </si>
 </sst>
 </file>
@@ -532,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F14"/>
+  <dimension ref="A2:G14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.125" style="1" bestFit="1" customWidth="1"/>
@@ -541,10 +547,11 @@
     <col min="4" max="4" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -563,8 +570,11 @@
       <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -583,8 +593,11 @@
       <c r="F3" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -603,8 +616,9 @@
       <c r="F4" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
@@ -623,8 +637,9 @@
       <c r="F5" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -643,8 +658,9 @@
       <c r="F6" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -663,8 +679,9 @@
       <c r="F7" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
@@ -683,8 +700,9 @@
       <c r="F8" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
@@ -703,8 +721,9 @@
       <c r="F9" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -721,8 +740,9 @@
       <c r="F10" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -741,8 +761,9 @@
       <c r="F11" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
@@ -759,8 +780,9 @@
       <c r="F12" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>45</v>
       </c>
@@ -777,8 +799,9 @@
       <c r="F13" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>46</v>
       </c>
@@ -791,6 +814,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A14">

--- a/Data/MaKho_MaVV.xlsx
+++ b/Data/MaKho_MaVV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_BB\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8BE4E8-3037-473A-9223-B8116E47A64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E47E7A-3514-46D9-A8D3-2D78516568E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,9 +45,6 @@
     <t>Dầu Điêzen 0,001S Mức 5</t>
   </si>
   <si>
-    <t>Kho TC SPDK Nam Định</t>
-  </si>
-  <si>
     <t>KHOTC01</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
     <t>HH0057</t>
   </si>
   <si>
-    <t>PVOIL ĐÌNH VŨ</t>
-  </si>
-  <si>
     <t>KHO2</t>
   </si>
   <si>
@@ -114,9 +108,6 @@
     <t>HH0059</t>
   </si>
   <si>
-    <t>NGHI SƠN</t>
-  </si>
-  <si>
     <t>KHO028</t>
   </si>
   <si>
@@ -132,9 +123,6 @@
     <t>HH005NS</t>
   </si>
   <si>
-    <t>CHÂN MÂY</t>
-  </si>
-  <si>
     <t>KHO023</t>
   </si>
   <si>
@@ -202,6 +190,18 @@
   </si>
   <si>
     <t>HH051-043</t>
+  </si>
+  <si>
+    <t>Kho Nam Định</t>
+  </si>
+  <si>
+    <t>Kho Đình Vũ</t>
+  </si>
+  <si>
+    <t>Kho Chân Mây</t>
+  </si>
+  <si>
+    <t>Kho Nghi Sơn</t>
   </si>
 </sst>
 </file>
@@ -571,246 +571,246 @@
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
